--- a/runs/RELX/2026-10-14/bear/scratch/gs_5yw_beta/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/gs_5yw_beta/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2438.177488266853</v>
+        <v>2485.595822294234</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.08289099999999999</v>
+        <v>0.0776102</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.07789518347456</v>
+        <v>0.07329127641856001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>12318.50906638888</v>
+        <v>12450.93973071</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>60335.72691835104</v>
+        <v>65892.29796011692</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>43050.6941649818</v>
+        <v>47929.78224883875</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>55369.20323137068</v>
+        <v>60380.72197954875</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>48372.20323137068</v>
+        <v>53383.72197954875</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>48213.50404511832</v>
+        <v>53330.46273503099</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>27.64924636394595</v>
+        <v>30.58369500553674</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2764.924636394595</v>
+        <v>3058.369500553674</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.0021924806</v>
+        <v>0.103706063</v>
       </c>
     </row>
   </sheetData>
